--- a/VCW.xlsx
+++ b/VCW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D76DD5-F33D-46CB-8F66-7888442DCDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E29CB8A-C163-495E-911E-8B2C26779AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D30F705F-2673-4493-98A8-D44649666D3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D30F705F-2673-4493-98A8-D44649666D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -54,7 +54,7 @@
     Mostly income from the port and some sales of PP&amp;E </t>
       </text>
     </comment>
-    <comment ref="L41" authorId="1" shapeId="0" xr:uid="{5FC0D63C-FD94-467E-97E6-8BE8E22FF089}">
+    <comment ref="L44" authorId="1" shapeId="0" xr:uid="{5FC0D63C-FD94-467E-97E6-8BE8E22FF089}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="110">
   <si>
     <t>Cement</t>
   </si>
@@ -330,9 +330,6 @@
     <t>Price 2030</t>
   </si>
   <si>
-    <t>Dividends ac.</t>
-  </si>
-  <si>
     <t>Current Price</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
     <t>Company will grow at very small stable rate (under the 8% of the last 7y)</t>
   </si>
   <si>
-    <t>Fairly conservative, although it dosen't account for taxes</t>
-  </si>
-  <si>
     <t>Dividends continue and payout at current rate (has been since 2014)</t>
   </si>
   <si>
@@ -379,6 +373,30 @@
   </si>
   <si>
     <t>Not a buying recommendation</t>
+  </si>
+  <si>
+    <t>% yield</t>
+  </si>
+  <si>
+    <t>Dividends inv.</t>
+  </si>
+  <si>
+    <t>Reinvesting the dividends at a 7% yield</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Constuction Materials</t>
+  </si>
+  <si>
+    <t>Fairly conservative, although without taxation</t>
+  </si>
+  <si>
+    <t>Fairly valued, would be a good dividend stock to park money in</t>
+  </si>
+  <si>
+    <t>Dividend (reinvested at yield)</t>
   </si>
 </sst>
 </file>
@@ -439,7 +457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -461,6 +479,7 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -805,7 +824,7 @@
   <threadedComment ref="J14" dT="2026-05-14T20:51:04.03" personId="{5FB1B16D-037D-4269-81FE-C552777B3F6B}" id="{48B3A57E-25A5-4E96-8941-0E4BBF63C337}">
     <text xml:space="preserve">Mostly income from the port and some sales of PP&amp;E </text>
   </threadedComment>
-  <threadedComment ref="L41" dT="2026-05-14T21:25:40.93" personId="{5FB1B16D-037D-4269-81FE-C552777B3F6B}" id="{5FC0D63C-FD94-467E-97E6-8BE8E22FF089}">
+  <threadedComment ref="L44" dT="2026-05-14T21:25:40.93" personId="{5FB1B16D-037D-4269-81FE-C552777B3F6B}" id="{5FC0D63C-FD94-467E-97E6-8BE8E22FF089}">
     <text>CY Gov bonds yield + CY ERP (damodaram)</text>
   </threadedComment>
 </ThreadedComments>
@@ -813,16 +832,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D048E23-C99B-4E6E-8BEE-4A0199F87E58}">
-  <dimension ref="C2:L24"/>
+  <dimension ref="C2:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="9" max="9" width="18.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H2" t="s">
         <v>68</v>
@@ -836,10 +856,10 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="K3" t="s">
         <v>20</v>
@@ -849,6 +869,12 @@
       <c r="C4" t="s">
         <v>74</v>
       </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
@@ -886,7 +912,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="1">
-        <f>Model!J56</f>
+        <f>Model!J59</f>
         <v>42184</v>
       </c>
     </row>
@@ -895,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="L9" s="1">
-        <f>Model!J70</f>
+        <f>Model!J73</f>
         <v>2198</v>
       </c>
     </row>
@@ -913,7 +939,7 @@
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
         <v>70</v>
@@ -922,7 +948,7 @@
         <v>59</v>
       </c>
       <c r="L12" s="4">
-        <f>L7/Model!J62</f>
+        <f>L7/Model!J65</f>
         <v>1.3117540014514264</v>
       </c>
     </row>
@@ -949,48 +975,53 @@
         <v>67</v>
       </c>
       <c r="L15" s="4">
-        <f>L7/Model!J78</f>
+        <f>L7/Model!J81</f>
         <v>1.3117540014514264</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="C24" s="14" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="C25" s="14" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1000,10 +1031,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A09068-5FEB-437D-8B49-F87FA9E19AE3}">
-  <dimension ref="A1:CQ252"/>
+  <dimension ref="A1:CQ255"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="9.125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.875" bestFit="1" customWidth="1"/>
@@ -2699,11 +2730,11 @@
         <v>0.69174811985929441</v>
       </c>
       <c r="AF32" s="7">
-        <f>AE32*(1+$M$40)</f>
+        <f>AE32*(1+$M$43)</f>
         <v>0.68483063866070149</v>
       </c>
       <c r="AG32" s="7">
-        <f t="shared" ref="AG32:CQ32" si="20">AF32*(1+$M$40)</f>
+        <f t="shared" ref="AG32:CQ32" si="20">AF32*(1+$M$43)</f>
         <v>0.67798233227409443</v>
       </c>
       <c r="AH32" s="7">
@@ -2985,11 +3016,11 @@
         <v>0.38</v>
       </c>
       <c r="K33" s="7">
-        <f>K32*K34</f>
+        <f>K32*K36</f>
         <v>0.35672560467055886</v>
       </c>
       <c r="L33" s="7">
-        <f t="shared" ref="L33:AE33" si="21">L32*L34</f>
+        <f t="shared" ref="L33:AE33" si="21">L32*L36</f>
         <v>0.37456188490408676</v>
       </c>
       <c r="M33" s="7">
@@ -3070,592 +3101,615 @@
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>66</v>
+      <c r="A34" t="s">
+        <v>109</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="7">
-        <f t="shared" ref="E34:I34" si="22">E33/E32</f>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7">
+        <f>K33*(1+K35)*(1+L35)*(1+M35)*(1+N35)*(1+O35)</f>
+        <v>0.5003261142156965</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" ref="L34:O34" si="22">L33*(1+L35)*(1+M35)*(1+N35)*(1+O35)*(1+P35)</f>
+        <v>0.49097422423035625</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="22"/>
+        <v>0.48179713592698525</v>
+      </c>
+      <c r="N34" s="7">
+        <f t="shared" si="22"/>
+        <v>0.47279158198442472</v>
+      </c>
+      <c r="O34" s="7">
+        <f t="shared" si="22"/>
+        <v>0.46395435615294017</v>
+      </c>
+      <c r="P34" s="7">
+        <f t="shared" ref="P34" si="23">P33*(1+P35)*(1+Q35)*(1+R35)*(1+S35)*(1+T35)</f>
+        <v>0.45528231211269832</v>
+      </c>
+      <c r="Q34" s="7">
+        <f t="shared" ref="Q34" si="24">Q33*(1+Q35)*(1+R35)*(1+S35)*(1+T35)*(1+U35)</f>
+        <v>0.47804642771833317</v>
+      </c>
+      <c r="R34" s="7">
+        <f t="shared" ref="R34" si="25">R33*(1+R35)*(1+S35)*(1+T35)*(1+U35)*(1+V35)</f>
+        <v>0.50194874910424991</v>
+      </c>
+      <c r="S34" s="7">
+        <f t="shared" ref="S34" si="26">S33*(1+S35)*(1+T35)*(1+U35)*(1+V35)*(1+W35)</f>
+        <v>0.52704618655946234</v>
+      </c>
+      <c r="T34" s="7">
+        <f t="shared" ref="T34" si="27">T33*(1+T35)*(1+U35)*(1+V35)*(1+W35)*(1+X35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="U34" s="7">
+        <f t="shared" ref="U34" si="28">U33*(1+U35)*(1+V35)*(1+W35)*(1+X35)*(1+Y35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="V34" s="7">
+        <f t="shared" ref="V34" si="29">V33*(1+V35)*(1+W35)*(1+X35)*(1+Y35)*(1+Z35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="W34" s="7">
+        <f t="shared" ref="W34" si="30">W33*(1+W35)*(1+X35)*(1+Y35)*(1+Z35)*(1+AA35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="X34" s="7">
+        <f t="shared" ref="X34" si="31">X33*(1+X35)*(1+Y35)*(1+Z35)*(1+AA35)*(1+AB35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="Y34" s="7">
+        <f t="shared" ref="Y34" si="32">Y33*(1+Y35)*(1+Z35)*(1+AA35)*(1+AB35)*(1+AC35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="Z34" s="7">
+        <f t="shared" ref="Z34" si="33">Z33*(1+Z35)*(1+AA35)*(1+AB35)*(1+AC35)*(1+AD35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="AA34" s="7">
+        <f t="shared" ref="AA34" si="34">AA33*(1+AA35)*(1+AB35)*(1+AC35)*(1+AD35)*(1+AE35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="AB34" s="7">
+        <f t="shared" ref="AB34" si="35">AB33*(1+AB35)*(1+AC35)*(1+AD35)*(1+AE35)*(1+AF35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="AC34" s="7">
+        <f t="shared" ref="AC34" si="36">AC33*(1+AC35)*(1+AD35)*(1+AE35)*(1+AF35)*(1+AG35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="AD34" s="7">
+        <f t="shared" ref="AD34" si="37">AD33*(1+AD35)*(1+AE35)*(1+AF35)*(1+AG35)*(1+AH35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+      <c r="AE34" s="7">
+        <f t="shared" ref="AE34" si="38">AE33*(1+AE35)*(1+AF35)*(1+AG35)*(1+AH35)*(1+AI35)</f>
+        <v>0.5533984958874355</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L35" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M35" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N35" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O35" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="7"/>
+      <c r="AE35" s="7"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="7">
+        <f t="shared" ref="E36:I36" si="39">E33/E32</f>
         <v>0.60377675199328584</v>
       </c>
-      <c r="F34" s="7">
-        <f t="shared" si="22"/>
+      <c r="F36" s="7">
+        <f t="shared" si="39"/>
         <v>0.86620033254973916</v>
       </c>
-      <c r="G34" s="7">
-        <f t="shared" si="22"/>
+      <c r="G36" s="7">
+        <f t="shared" si="39"/>
         <v>1.0747444566755779</v>
       </c>
-      <c r="H34" s="7">
-        <f t="shared" si="22"/>
+      <c r="H36" s="7">
+        <f t="shared" si="39"/>
         <v>0.54265086206896551</v>
       </c>
-      <c r="I34" s="7">
-        <f t="shared" si="22"/>
+      <c r="I36" s="7">
+        <f t="shared" si="39"/>
         <v>0.80609713689579232</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J36" s="7">
         <f>J33/J32</f>
         <v>0.76947673600360289</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K36" s="10">
         <v>0.8</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L36" s="10">
         <v>0.8</v>
       </c>
-      <c r="M34" s="10">
+      <c r="M36" s="10">
         <v>0.8</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N36" s="10">
         <v>0.8</v>
       </c>
-      <c r="O34" s="10">
+      <c r="O36" s="10">
         <v>0.8</v>
       </c>
-      <c r="P34" s="10">
+      <c r="P36" s="10">
         <v>0.8</v>
       </c>
-      <c r="Q34" s="10">
+      <c r="Q36" s="10">
         <v>0.8</v>
       </c>
-      <c r="R34" s="10">
+      <c r="R36" s="10">
         <v>0.8</v>
       </c>
-      <c r="S34" s="10">
+      <c r="S36" s="10">
         <v>0.8</v>
       </c>
-      <c r="T34" s="10">
+      <c r="T36" s="10">
         <v>0.8</v>
       </c>
-      <c r="U34" s="10">
+      <c r="U36" s="10">
         <v>0.8</v>
       </c>
-      <c r="V34" s="10">
+      <c r="V36" s="10">
         <v>0.8</v>
       </c>
-      <c r="W34" s="10">
+      <c r="W36" s="10">
         <v>0.8</v>
       </c>
-      <c r="X34" s="10">
+      <c r="X36" s="10">
         <v>0.8</v>
       </c>
-      <c r="Y34" s="10">
+      <c r="Y36" s="10">
         <v>0.8</v>
       </c>
-      <c r="Z34" s="10">
+      <c r="Z36" s="10">
         <v>0.8</v>
       </c>
-      <c r="AA34" s="10">
+      <c r="AA36" s="10">
         <v>0.8</v>
       </c>
-      <c r="AB34" s="10">
+      <c r="AB36" s="10">
         <v>0.8</v>
       </c>
-      <c r="AC34" s="10">
+      <c r="AC36" s="10">
         <v>0.8</v>
       </c>
-      <c r="AD34" s="10">
+      <c r="AD36" s="10">
         <v>0.8</v>
       </c>
-      <c r="AE34" s="10">
+      <c r="AE36" s="10">
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36">
-        <v>13939</v>
-      </c>
-      <c r="F36">
-        <v>14258</v>
-      </c>
-      <c r="G36">
-        <v>15253</v>
-      </c>
-      <c r="H36">
-        <v>14255</v>
-      </c>
-      <c r="I36">
-        <v>14251</v>
-      </c>
-      <c r="J36">
-        <v>14196</v>
-      </c>
-      <c r="K36" s="11"/>
-    </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>53</v>
-      </c>
+      <c r="A37" s="2"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37">
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
+      <c r="AA37" s="10"/>
+      <c r="AB37" s="10"/>
+      <c r="AC37" s="10"/>
+      <c r="AD37" s="10"/>
+      <c r="AE37" s="10"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39">
+        <v>13939</v>
+      </c>
+      <c r="F39">
+        <v>14258</v>
+      </c>
+      <c r="G39">
+        <v>15253</v>
+      </c>
+      <c r="H39">
+        <v>14255</v>
+      </c>
+      <c r="I39">
+        <v>14251</v>
+      </c>
+      <c r="J39">
+        <v>14196</v>
+      </c>
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40">
         <f>-608+5217-1046</f>
         <v>3563</v>
       </c>
-      <c r="F37">
+      <c r="F40">
         <f>972-16366-502</f>
         <v>-15896</v>
       </c>
-      <c r="G37">
+      <c r="G40">
         <f>-5648-4154+5421-300</f>
         <v>-4681</v>
       </c>
-      <c r="H37">
+      <c r="H40">
         <f>1766-1100-1303</f>
         <v>-637</v>
       </c>
-      <c r="I37">
+      <c r="I40">
         <f>890-587-2317</f>
         <v>-2014</v>
       </c>
-      <c r="J37">
+      <c r="J40">
         <f>-1416+5512+465</f>
         <v>4561</v>
       </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38">
-        <v>-10886</v>
-      </c>
-      <c r="F38">
-        <v>-9925</v>
-      </c>
-      <c r="G38">
-        <v>-10490</v>
-      </c>
-      <c r="H38">
-        <v>-5934</v>
-      </c>
-      <c r="I38">
-        <v>-6876</v>
-      </c>
-      <c r="J38">
-        <v>-9966</v>
-      </c>
-      <c r="O38" s="7"/>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <f>E28+SUM(E36:E38)</f>
-        <v>23297</v>
-      </c>
-      <c r="F39" s="1">
-        <f>F28+SUM(F36:F38)</f>
-        <v>5878</v>
-      </c>
-      <c r="G39" s="1">
-        <f>G28+SUM(G36:G38)</f>
-        <v>12800</v>
-      </c>
-      <c r="H39" s="1">
-        <f>H28+SUM(H36:H38)</f>
-        <v>35524</v>
-      </c>
-      <c r="I39" s="1">
-        <f t="shared" ref="I39:J39" si="23">I28+SUM(I36:I38)</f>
-        <v>31242</v>
-      </c>
-      <c r="J39" s="1">
-        <f t="shared" si="23"/>
-        <v>44318</v>
-      </c>
-      <c r="K39" s="1"/>
-      <c r="L39" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" t="s">
-        <v>89</v>
-      </c>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="3">
-        <f t="shared" ref="E40:J40" si="24">E39/E7</f>
-        <v>0.22048816498045637</v>
-      </c>
-      <c r="F40" s="3">
-        <f t="shared" si="24"/>
-        <v>5.7957581912659366E-2</v>
-      </c>
-      <c r="G40" s="3">
-        <f t="shared" si="24"/>
-        <v>8.9723189939787326E-2</v>
-      </c>
-      <c r="H40" s="3">
-        <f t="shared" si="24"/>
-        <v>0.22128921336555951</v>
-      </c>
-      <c r="I40" s="3">
-        <f t="shared" si="24"/>
-        <v>0.22674785713767301</v>
-      </c>
-      <c r="J40" s="3">
-        <f t="shared" si="24"/>
-        <v>0.29012470950214397</v>
-      </c>
-      <c r="K40" s="9"/>
-      <c r="L40" t="s">
-        <v>77</v>
-      </c>
-      <c r="M40" s="3">
-        <v>-0.01</v>
-      </c>
-      <c r="P40" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="L41" t="s">
-        <v>76</v>
-      </c>
-      <c r="M41" s="3">
-        <f>0.0348+0.0578</f>
-        <v>9.2599999999999988E-2</v>
-      </c>
-      <c r="P41" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q41" s="8">
-        <f>Q40*O32</f>
-        <v>5.4200275251511698</v>
-      </c>
+      <c r="E41">
+        <v>-10886</v>
+      </c>
+      <c r="F41">
+        <v>-9925</v>
+      </c>
+      <c r="G41">
+        <v>-10490</v>
+      </c>
+      <c r="H41">
+        <v>-5934</v>
+      </c>
+      <c r="I41">
+        <v>-6876</v>
+      </c>
+      <c r="J41">
+        <v>-9966</v>
+      </c>
+      <c r="O41" s="7"/>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M42" s="5">
-        <f>NPV(M41,K32:CQ32)</f>
-        <v>6.3901828530534033</v>
-      </c>
-      <c r="P42" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q42" s="8">
-        <f>SUM(K33:O33)</f>
-        <v>1.9711341488427863</v>
-      </c>
+      <c r="E42" s="1">
+        <f>E28+SUM(E39:E41)</f>
+        <v>23297</v>
+      </c>
+      <c r="F42" s="1">
+        <f>F28+SUM(F39:F41)</f>
+        <v>5878</v>
+      </c>
+      <c r="G42" s="1">
+        <f>G28+SUM(G39:G41)</f>
+        <v>12800</v>
+      </c>
+      <c r="H42" s="1">
+        <f>H28+SUM(H39:H41)</f>
+        <v>35524</v>
+      </c>
+      <c r="I42" s="1">
+        <f t="shared" ref="I42:J42" si="40">I28+SUM(I39:I41)</f>
+        <v>31242</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="40"/>
+        <v>44318</v>
+      </c>
+      <c r="K42" s="1"/>
+      <c r="L42" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
       <c r="S42" t="s">
-        <v>99</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="K43" s="5"/>
+      <c r="E43" s="3">
+        <f t="shared" ref="E43:J43" si="41">E42/E7</f>
+        <v>0.22048816498045637</v>
+      </c>
+      <c r="F43" s="3">
+        <f t="shared" si="41"/>
+        <v>5.7957581912659366E-2</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="41"/>
+        <v>8.9723189939787326E-2</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="41"/>
+        <v>0.22128921336555951</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="41"/>
+        <v>0.22674785713767301</v>
+      </c>
+      <c r="J43" s="3">
+        <f t="shared" si="41"/>
+        <v>0.29012470950214397</v>
+      </c>
+      <c r="K43" s="9"/>
       <c r="L43" t="s">
-        <v>79</v>
-      </c>
-      <c r="M43">
-        <v>5</v>
+        <v>77</v>
+      </c>
+      <c r="M43" s="3">
+        <v>-0.01</v>
       </c>
       <c r="P43" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>5</v>
-      </c>
-      <c r="S43" t="s">
-        <v>90</v>
+        <v>85</v>
+      </c>
+      <c r="Q43">
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="L44" t="s">
-        <v>80</v>
-      </c>
-      <c r="M44" s="10">
-        <f>M42/M43-1</f>
-        <v>0.27803657061068066</v>
+        <v>76</v>
+      </c>
+      <c r="M44" s="3">
+        <f>0.0348+0.0578</f>
+        <v>9.2599999999999988E-2</v>
       </c>
       <c r="P44" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q44" s="10">
-        <f>Q41/Q43-1</f>
-        <v>8.4005505030233962E-2</v>
-      </c>
-      <c r="S44" t="s">
-        <v>101</v>
+        <v>86</v>
+      </c>
+      <c r="Q44" s="8">
+        <f>Q43*O32</f>
+        <v>5.4200275251511698</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>27</v>
-      </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45">
-        <v>226107</v>
-      </c>
-      <c r="F45" s="1">
-        <v>221837</v>
-      </c>
-      <c r="G45" s="1">
-        <v>213249</v>
-      </c>
-      <c r="H45" s="1">
-        <v>200381</v>
-      </c>
-      <c r="I45" s="1">
-        <v>193640</v>
-      </c>
-      <c r="J45" s="1">
-        <v>189320</v>
-      </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M45" s="10">
-        <f>(Q42+M42)/M43</f>
-        <v>1.6722634003792378</v>
-      </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45" s="5">
+        <f>NPV(M44,K32:CQ32)</f>
+        <v>6.3901828530534033</v>
+      </c>
       <c r="P45" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q45" s="10">
-        <f>(Q41+Q42)/Q43-1</f>
-        <v>0.47823233479879113</v>
-      </c>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="1"/>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="Q45" s="8">
+        <f>SUM(K34:O34)</f>
+        <v>2.4098434125104031</v>
+      </c>
+      <c r="S45" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>28</v>
-      </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46">
-        <v>12363</v>
-      </c>
-      <c r="F46" s="1">
-        <v>12332</v>
-      </c>
-      <c r="G46" s="1">
-        <v>12338</v>
-      </c>
-      <c r="H46" s="1">
-        <v>12336</v>
-      </c>
-      <c r="I46" s="1">
-        <v>12344</v>
-      </c>
-      <c r="J46" s="1">
-        <v>12342</v>
-      </c>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M46" s="10">
-        <f>((M42+Q42)/M43)^(1/5)-1</f>
-        <v>0.10830919657182858</v>
-      </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q46" s="10">
-        <f>((Q41+Q42)/Q43)^(1/5)-1</f>
-        <v>8.1305817566158511E-2</v>
-      </c>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
+      <c r="K46" s="5"/>
+      <c r="L46" t="s">
+        <v>79</v>
+      </c>
+      <c r="M46">
+        <v>5</v>
+      </c>
+      <c r="P46" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>5</v>
+      </c>
+      <c r="S46" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47">
-        <v>5583</v>
-      </c>
-      <c r="F47" s="1">
-        <v>5533</v>
-      </c>
-      <c r="G47" s="1">
-        <v>5608</v>
-      </c>
-      <c r="H47" s="1">
-        <v>10187</v>
-      </c>
-      <c r="I47" s="1">
-        <v>10309</v>
-      </c>
-      <c r="J47" s="1">
-        <v>10318</v>
-      </c>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
+      <c r="L47" t="s">
+        <v>80</v>
+      </c>
+      <c r="M47" s="10">
+        <f>M45/M46-1</f>
+        <v>0.27803657061068066</v>
+      </c>
+      <c r="P47" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q47" s="10">
+        <f>Q44/Q46-1</f>
+        <v>8.4005505030233962E-2</v>
+      </c>
+      <c r="S47" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48">
-        <v>1700</v>
+        <v>226107</v>
       </c>
       <c r="F48" s="1">
-        <v>1583</v>
+        <v>221837</v>
       </c>
       <c r="G48" s="1">
-        <v>2508</v>
+        <v>213249</v>
       </c>
       <c r="H48" s="1">
-        <v>2377</v>
+        <v>200381</v>
       </c>
       <c r="I48" s="1">
-        <v>2236</v>
+        <v>193640</v>
       </c>
       <c r="J48" s="1">
-        <v>2099</v>
-      </c>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+        <v>189320</v>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M48" s="10">
+        <f>(Q45+M45)/M46</f>
+        <v>1.7600052531127612</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="10"/>
+      <c r="P48" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q48" s="10">
+        <f>(Q44+Q45)/Q46-1</f>
+        <v>0.56597418753231454</v>
+      </c>
       <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
+      <c r="S48" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
@@ -3671,37 +3725,49 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49">
-        <v>1560</v>
+        <v>12363</v>
       </c>
       <c r="F49" s="1">
-        <v>1625</v>
+        <v>12332</v>
       </c>
       <c r="G49" s="1">
-        <v>1697</v>
+        <v>12338</v>
       </c>
       <c r="H49" s="1">
-        <v>1842</v>
+        <v>12336</v>
       </c>
       <c r="I49" s="1">
-        <v>2022</v>
+        <v>12344</v>
       </c>
       <c r="J49" s="1">
-        <v>2147</v>
+        <v>12342</v>
       </c>
       <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
+      <c r="L49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M49" s="15">
+        <f>((M45+Q45)/M46)^(1/5)-1</f>
+        <v>0.11970287367985444</v>
+      </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
+      <c r="P49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q49" s="15">
+        <f>((Q44+Q45)/Q46)^(1/5)-1</f>
+        <v>9.3847855830024862E-2</v>
+      </c>
       <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
+      <c r="S49" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
@@ -3717,35 +3783,35 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50">
-        <v>218</v>
+        <v>5583</v>
       </c>
       <c r="F50" s="1">
-        <v>232</v>
+        <v>5533</v>
       </c>
       <c r="G50" s="1">
-        <v>280</v>
+        <v>5608</v>
       </c>
       <c r="H50" s="1">
-        <v>363</v>
+        <v>10187</v>
       </c>
       <c r="I50" s="1">
-        <v>304</v>
+        <v>10309</v>
       </c>
       <c r="J50" s="1">
-        <v>350</v>
+        <v>10318</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
+      <c r="M50" s="10"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+      <c r="Q50" s="10"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
@@ -3763,33 +3829,27 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1">
-        <f t="shared" ref="E51:H51" si="25">SUM(E45:E50)</f>
-        <v>247531</v>
+      <c r="E51">
+        <v>1700</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" si="25"/>
-        <v>243142</v>
+        <v>1583</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" si="25"/>
-        <v>235680</v>
+        <v>2508</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="25"/>
-        <v>227486</v>
+        <v>2377</v>
       </c>
       <c r="I51" s="1">
-        <f>SUM(I45:I50)</f>
-        <v>220855</v>
+        <v>2236</v>
       </c>
       <c r="J51" s="1">
-        <f>SUM(J45:J50)</f>
-        <v>216576</v>
+        <v>2099</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -3797,8 +3857,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
+      <c r="Q51" s="10"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
@@ -3814,13 +3873,29 @@
       <c r="AE51" s="1"/>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
+      <c r="E52">
+        <v>1560</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1625</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1697</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1842</v>
+      </c>
+      <c r="I52" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2147</v>
+      </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -3845,27 +3920,27 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53">
-        <v>25712</v>
+        <v>218</v>
       </c>
       <c r="F53" s="1">
-        <v>42078</v>
+        <v>232</v>
       </c>
       <c r="G53" s="1">
-        <v>46232</v>
+        <v>280</v>
       </c>
       <c r="H53" s="1">
-        <v>47332</v>
+        <v>363</v>
       </c>
       <c r="I53" s="1">
-        <v>47130</v>
+        <v>304</v>
       </c>
       <c r="J53" s="1">
-        <v>41618</v>
+        <v>350</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -3891,18 +3966,33 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="E54" s="1">
+        <f t="shared" ref="E54:H54" si="42">SUM(E48:E53)</f>
+        <v>247531</v>
+      </c>
+      <c r="F54" s="1">
+        <f t="shared" si="42"/>
+        <v>243142</v>
+      </c>
+      <c r="G54" s="1">
+        <f t="shared" si="42"/>
+        <v>235680</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="42"/>
+        <v>227486</v>
+      </c>
       <c r="I54" s="1">
-        <v>165</v>
+        <f>SUM(I48:I53)</f>
+        <v>220855</v>
       </c>
       <c r="J54" s="1">
-        <v>165</v>
+        <f>SUM(J48:J53)</f>
+        <v>216576</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3927,29 +4017,13 @@
       <c r="AE54" s="1"/>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>35</v>
-      </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55">
-        <v>7630</v>
-      </c>
-      <c r="F55" s="1">
-        <v>6885</v>
-      </c>
-      <c r="G55" s="1">
-        <v>12607</v>
-      </c>
-      <c r="H55" s="1">
-        <v>11063</v>
-      </c>
-      <c r="I55" s="1">
-        <v>12389</v>
-      </c>
-      <c r="J55" s="1">
-        <v>14353</v>
-      </c>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -3974,27 +4048,27 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56">
-        <v>13782</v>
+        <v>25712</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>42078</v>
       </c>
       <c r="G56" s="1">
-        <v>2209</v>
+        <v>46232</v>
       </c>
       <c r="H56" s="1">
-        <v>18181</v>
+        <v>47332</v>
       </c>
       <c r="I56" s="1">
-        <v>25380</v>
+        <v>47130</v>
       </c>
       <c r="J56" s="1">
-        <v>42184</v>
+        <v>41618</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -4020,33 +4094,18 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="1">
-        <f t="shared" ref="E57" si="26">SUM(E53:E56)</f>
-        <v>47124</v>
-      </c>
-      <c r="F57" s="1">
-        <f t="shared" ref="F57:H57" si="27">SUM(F53:F56)</f>
-        <v>48963</v>
-      </c>
-      <c r="G57" s="1">
-        <f t="shared" si="27"/>
-        <v>61048</v>
-      </c>
-      <c r="H57" s="1">
-        <f t="shared" si="27"/>
-        <v>76576</v>
-      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
       <c r="I57" s="1">
-        <f>SUM(I53:I56)</f>
-        <v>85064</v>
+        <v>165</v>
       </c>
       <c r="J57" s="1">
-        <f>SUM(J53:J56)</f>
-        <v>98320</v>
+        <v>165</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -4072,33 +4131,27 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="1">
-        <f t="shared" ref="E58" si="28">E51+E57</f>
-        <v>294655</v>
+      <c r="E58">
+        <v>7630</v>
       </c>
       <c r="F58" s="1">
-        <f t="shared" ref="F58:I58" si="29">F51+F57</f>
-        <v>292105</v>
+        <v>6885</v>
       </c>
       <c r="G58" s="1">
-        <f t="shared" si="29"/>
-        <v>296728</v>
+        <v>12607</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="29"/>
-        <v>304062</v>
+        <v>11063</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="29"/>
-        <v>305919</v>
+        <v>12389</v>
       </c>
       <c r="J58" s="1">
-        <f>J51+J57</f>
-        <v>314896</v>
+        <v>14353</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -4123,13 +4176,29 @@
       <c r="AE58" s="1"/>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="E59">
+        <v>13782</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2209</v>
+      </c>
+      <c r="H59" s="1">
+        <v>18181</v>
+      </c>
+      <c r="I59" s="1">
+        <v>25380</v>
+      </c>
+      <c r="J59" s="1">
+        <v>42184</v>
+      </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -4154,27 +4223,33 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1">
-        <v>30932</v>
+        <f t="shared" ref="E60" si="43">SUM(E56:E59)</f>
+        <v>47124</v>
       </c>
       <c r="F60" s="1">
-        <v>30932</v>
+        <f t="shared" ref="F60:H60" si="44">SUM(F56:F59)</f>
+        <v>48963</v>
       </c>
       <c r="G60" s="1">
-        <v>30932</v>
+        <f t="shared" si="44"/>
+        <v>61048</v>
       </c>
       <c r="H60" s="1">
-        <v>30932</v>
+        <f t="shared" si="44"/>
+        <v>76576</v>
       </c>
       <c r="I60" s="1">
-        <v>30932</v>
+        <f>SUM(I56:I59)</f>
+        <v>85064</v>
       </c>
       <c r="J60" s="1">
-        <v>30932</v>
+        <f>SUM(J56:J59)</f>
+        <v>98320</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -4200,27 +4275,33 @@
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61">
-        <v>216133</v>
+      <c r="E61" s="1">
+        <f t="shared" ref="E61" si="45">E54+E60</f>
+        <v>294655</v>
       </c>
       <c r="F61" s="1">
-        <v>216654</v>
+        <f t="shared" ref="F61:I61" si="46">F54+F60</f>
+        <v>292105</v>
       </c>
       <c r="G61" s="1">
-        <v>213497</v>
+        <f t="shared" si="46"/>
+        <v>296728</v>
       </c>
       <c r="H61" s="1">
-        <v>226312</v>
+        <f t="shared" si="46"/>
+        <v>304062</v>
       </c>
       <c r="I61" s="1">
-        <v>231446</v>
+        <f t="shared" si="46"/>
+        <v>305919</v>
       </c>
       <c r="J61" s="1">
-        <v>243281</v>
+        <f>J54+J60</f>
+        <v>314896</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -4245,35 +4326,13 @@
       <c r="AE61" s="1"/>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>41</v>
-      </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="1">
-        <f t="shared" ref="E62:I62" si="30">E60+E61</f>
-        <v>247065</v>
-      </c>
-      <c r="F62" s="1">
-        <f t="shared" si="30"/>
-        <v>247586</v>
-      </c>
-      <c r="G62" s="1">
-        <f t="shared" si="30"/>
-        <v>244429</v>
-      </c>
-      <c r="H62" s="1">
-        <f t="shared" si="30"/>
-        <v>257244</v>
-      </c>
-      <c r="I62" s="1">
-        <f t="shared" si="30"/>
-        <v>262378</v>
-      </c>
-      <c r="J62" s="1">
-        <f>J60+J61</f>
-        <v>274213</v>
-      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -4297,13 +4356,29 @@
       <c r="AE62" s="1"/>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>39</v>
+      </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="E63" s="1">
+        <v>30932</v>
+      </c>
+      <c r="F63" s="1">
+        <v>30932</v>
+      </c>
+      <c r="G63" s="1">
+        <v>30932</v>
+      </c>
+      <c r="H63" s="1">
+        <v>30932</v>
+      </c>
+      <c r="I63" s="1">
+        <v>30932</v>
+      </c>
+      <c r="J63" s="1">
+        <v>30932</v>
+      </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -4328,27 +4403,27 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64">
-        <v>4760</v>
+        <v>216133</v>
       </c>
       <c r="F64" s="1">
-        <v>3801</v>
+        <v>216654</v>
       </c>
       <c r="G64" s="1">
-        <v>12249</v>
+        <v>213497</v>
       </c>
       <c r="H64" s="1">
-        <v>9023</v>
+        <v>226312</v>
       </c>
       <c r="I64" s="1">
-        <v>5703</v>
+        <v>231446</v>
       </c>
       <c r="J64" s="1">
-        <v>3651</v>
+        <v>243281</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -4374,27 +4449,33 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65">
-        <v>1605</v>
+      <c r="E65" s="1">
+        <f t="shared" ref="E65:I65" si="47">E63+E64</f>
+        <v>247065</v>
       </c>
       <c r="F65" s="1">
-        <v>1542</v>
+        <f t="shared" si="47"/>
+        <v>247586</v>
       </c>
       <c r="G65" s="1">
-        <v>1471</v>
+        <f t="shared" si="47"/>
+        <v>244429</v>
       </c>
       <c r="H65" s="1">
-        <v>1412</v>
+        <f t="shared" si="47"/>
+        <v>257244</v>
       </c>
       <c r="I65" s="1">
-        <v>1320</v>
+        <f t="shared" si="47"/>
+        <v>262378</v>
       </c>
       <c r="J65" s="1">
-        <v>1205</v>
+        <f>J63+J64</f>
+        <v>274213</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -4419,29 +4500,13 @@
       <c r="AE65" s="1"/>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>44</v>
-      </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
-      <c r="E66">
-        <v>25182</v>
-      </c>
-      <c r="F66" s="1">
-        <v>23910</v>
-      </c>
-      <c r="G66" s="1">
-        <v>22611</v>
-      </c>
-      <c r="H66" s="1">
-        <v>21472</v>
-      </c>
-      <c r="I66" s="1">
-        <v>20349</v>
-      </c>
-      <c r="J66" s="1">
-        <v>22172</v>
-      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -4466,20 +4531,28 @@
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="1">
-        <v>300</v>
+      <c r="E67">
+        <v>4760</v>
       </c>
       <c r="F67" s="1">
-        <v>300</v>
-      </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+        <v>3801</v>
+      </c>
+      <c r="G67" s="1">
+        <v>12249</v>
+      </c>
+      <c r="H67" s="1">
+        <v>9023</v>
+      </c>
+      <c r="I67" s="1">
+        <v>5703</v>
+      </c>
+      <c r="J67" s="1">
+        <v>3651</v>
+      </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -4504,33 +4577,27 @@
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="1">
-        <f>SUM(E64:E67)</f>
-        <v>31847</v>
+      <c r="E68">
+        <v>1605</v>
       </c>
       <c r="F68" s="1">
-        <f>SUM(F64:F67)</f>
-        <v>29553</v>
+        <v>1542</v>
       </c>
       <c r="G68" s="1">
-        <f t="shared" ref="G68:J68" si="31">SUM(G64:G67)</f>
-        <v>36331</v>
+        <v>1471</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="31"/>
-        <v>31907</v>
+        <v>1412</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" si="31"/>
-        <v>27372</v>
+        <v>1320</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="31"/>
-        <v>27028</v>
+        <v>1205</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -4555,13 +4622,29 @@
       <c r="AE68" s="1"/>
     </row>
     <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="E69">
+        <v>25182</v>
+      </c>
+      <c r="F69" s="1">
+        <v>23910</v>
+      </c>
+      <c r="G69" s="1">
+        <v>22611</v>
+      </c>
+      <c r="H69" s="1">
+        <v>21472</v>
+      </c>
+      <c r="I69" s="1">
+        <v>20349</v>
+      </c>
+      <c r="J69" s="1">
+        <v>22172</v>
+      </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -4586,29 +4669,20 @@
     </row>
     <row r="70" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
-      <c r="E70">
-        <v>8181</v>
+      <c r="E70" s="1">
+        <v>300</v>
       </c>
       <c r="F70" s="1">
-        <f>6149+959</f>
-        <v>7108</v>
-      </c>
-      <c r="G70" s="1">
-        <v>3454</v>
-      </c>
-      <c r="H70" s="1">
-        <v>3501</v>
-      </c>
-      <c r="I70" s="1">
-        <v>2599</v>
-      </c>
-      <c r="J70" s="1">
-        <v>2198</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -4633,27 +4707,33 @@
     </row>
     <row r="71" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71">
-        <v>121</v>
+      <c r="E71" s="1">
+        <f>SUM(E67:E70)</f>
+        <v>31847</v>
       </c>
       <c r="F71" s="1">
-        <v>115</v>
+        <f>SUM(F67:F70)</f>
+        <v>29553</v>
       </c>
       <c r="G71" s="1">
-        <v>115</v>
+        <f t="shared" ref="G71:J71" si="48">SUM(G67:G70)</f>
+        <v>36331</v>
       </c>
       <c r="H71" s="1">
-        <v>116</v>
+        <f t="shared" si="48"/>
+        <v>31907</v>
       </c>
       <c r="I71" s="1">
-        <v>132</v>
+        <f t="shared" si="48"/>
+        <v>27372</v>
       </c>
       <c r="J71" s="1">
-        <v>152</v>
+        <f t="shared" si="48"/>
+        <v>27028</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -4678,29 +4758,13 @@
       <c r="AE71" s="1"/>
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>45</v>
-      </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
-      <c r="E72">
-        <v>70</v>
-      </c>
-      <c r="F72" s="1">
-        <v>875</v>
-      </c>
-      <c r="G72" s="1">
-        <v>200</v>
-      </c>
-      <c r="H72" s="1">
-        <v>432</v>
-      </c>
-      <c r="I72" s="1">
-        <v>3037</v>
-      </c>
-      <c r="J72" s="1">
-        <v>455</v>
-      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -4725,27 +4789,28 @@
     </row>
     <row r="73" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73">
-        <v>7371</v>
+        <v>8181</v>
       </c>
       <c r="F73" s="1">
-        <v>6868</v>
+        <f>6149+959</f>
+        <v>7108</v>
       </c>
       <c r="G73" s="1">
-        <v>12199</v>
+        <v>3454</v>
       </c>
       <c r="H73" s="1">
-        <v>10862</v>
+        <v>3501</v>
       </c>
       <c r="I73" s="1">
-        <v>10401</v>
+        <v>2599</v>
       </c>
       <c r="J73" s="1">
-        <v>10850</v>
+        <v>2198</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -4771,33 +4836,27 @@
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="1">
-        <f t="shared" ref="E74:F74" si="32">SUM(E70:E73)</f>
-        <v>15743</v>
+      <c r="E74">
+        <v>121</v>
       </c>
       <c r="F74" s="1">
-        <f t="shared" si="32"/>
-        <v>14966</v>
+        <v>115</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" ref="G74:I74" si="33">SUM(G70:G73)</f>
-        <v>15968</v>
+        <v>115</v>
       </c>
       <c r="H74" s="1">
-        <f t="shared" si="33"/>
-        <v>14911</v>
+        <v>116</v>
       </c>
       <c r="I74" s="1">
-        <f t="shared" si="33"/>
-        <v>16169</v>
+        <v>132</v>
       </c>
       <c r="J74" s="1">
-        <f>SUM(J70:J73)</f>
-        <v>13655</v>
+        <v>152</v>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -4823,33 +4882,27 @@
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="1">
-        <f t="shared" ref="E75:F75" si="34">E68+E74</f>
-        <v>47590</v>
+      <c r="E75">
+        <v>70</v>
       </c>
       <c r="F75" s="1">
-        <f t="shared" si="34"/>
-        <v>44519</v>
+        <v>875</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" ref="G75:I75" si="35">G68+G74</f>
-        <v>52299</v>
+        <v>200</v>
       </c>
       <c r="H75" s="1">
-        <f t="shared" si="35"/>
-        <v>46818</v>
+        <v>432</v>
       </c>
       <c r="I75" s="1">
-        <f t="shared" si="35"/>
-        <v>43541</v>
+        <v>3037</v>
       </c>
       <c r="J75" s="1">
-        <f>J68+J74</f>
-        <v>40683</v>
+        <v>455</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -4875,33 +4928,27 @@
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="1">
-        <f t="shared" ref="E76:F76" si="36">E62+E75</f>
-        <v>294655</v>
+      <c r="E76">
+        <v>7371</v>
       </c>
       <c r="F76" s="1">
-        <f t="shared" si="36"/>
-        <v>292105</v>
+        <v>6868</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" ref="G76:I76" si="37">G62+G75</f>
-        <v>296728</v>
+        <v>12199</v>
       </c>
       <c r="H76" s="1">
-        <f t="shared" si="37"/>
-        <v>304062</v>
+        <v>10862</v>
       </c>
       <c r="I76" s="1">
-        <f t="shared" si="37"/>
-        <v>305919</v>
+        <v>10401</v>
       </c>
       <c r="J76" s="1">
-        <f>J62+J75</f>
-        <v>314896</v>
+        <v>10850</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -4926,13 +4973,35 @@
       <c r="AE76" s="1"/>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>37</v>
+      </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="E77" s="1">
+        <f t="shared" ref="E77:F77" si="49">SUM(E73:E76)</f>
+        <v>15743</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" si="49"/>
+        <v>14966</v>
+      </c>
+      <c r="G77" s="1">
+        <f t="shared" ref="G77:I77" si="50">SUM(G73:G76)</f>
+        <v>15968</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="50"/>
+        <v>14911</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="50"/>
+        <v>16169</v>
+      </c>
+      <c r="J77" s="1">
+        <f>SUM(J73:J76)</f>
+        <v>13655</v>
+      </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -4957,33 +5026,33 @@
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1">
-        <f t="shared" ref="E78:F78" si="38">E58-E75</f>
-        <v>247065</v>
+        <f t="shared" ref="E78:F78" si="51">E71+E77</f>
+        <v>47590</v>
       </c>
       <c r="F78" s="1">
-        <f t="shared" si="38"/>
-        <v>247586</v>
+        <f t="shared" si="51"/>
+        <v>44519</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" ref="G78:I78" si="39">G58-G75</f>
-        <v>244429</v>
+        <f t="shared" ref="G78:I78" si="52">G71+G77</f>
+        <v>52299</v>
       </c>
       <c r="H78" s="1">
-        <f t="shared" si="39"/>
-        <v>257244</v>
+        <f t="shared" si="52"/>
+        <v>46818</v>
       </c>
       <c r="I78" s="1">
-        <f t="shared" si="39"/>
-        <v>262378</v>
+        <f t="shared" si="52"/>
+        <v>43541</v>
       </c>
       <c r="J78" s="1">
-        <f>J58-J75</f>
-        <v>274213</v>
+        <f>J71+J77</f>
+        <v>40683</v>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -5009,33 +5078,33 @@
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1">
-        <f t="shared" ref="E79:F79" si="40">E57-E75</f>
-        <v>-466</v>
+        <f t="shared" ref="E79:F79" si="53">E65+E78</f>
+        <v>294655</v>
       </c>
       <c r="F79" s="1">
-        <f t="shared" si="40"/>
-        <v>4444</v>
+        <f t="shared" si="53"/>
+        <v>292105</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" ref="G79:H79" si="41">G57-G75</f>
-        <v>8749</v>
+        <f t="shared" ref="G79:I79" si="54">G65+G78</f>
+        <v>296728</v>
       </c>
       <c r="H79" s="1">
-        <f t="shared" si="41"/>
-        <v>29758</v>
+        <f t="shared" si="54"/>
+        <v>304062</v>
       </c>
       <c r="I79" s="1">
-        <f>I57-I75</f>
-        <v>41523</v>
+        <f t="shared" si="54"/>
+        <v>305919</v>
       </c>
       <c r="J79" s="1">
-        <f>J57-J75</f>
-        <v>57637</v>
+        <f>J65+J78</f>
+        <v>314896</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -5060,6 +5129,8 @@
       <c r="AE79" s="1"/>
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -5087,12 +5158,36 @@
       <c r="AD80" s="1"/>
       <c r="AE80" s="1"/>
     </row>
-    <row r="81" spans="6:31" x14ac:dyDescent="0.2">
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1">
+        <f t="shared" ref="E81:F81" si="55">E61-E78</f>
+        <v>247065</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="55"/>
+        <v>247586</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" ref="G81:I81" si="56">G61-G78</f>
+        <v>244429</v>
+      </c>
+      <c r="H81" s="1">
+        <f t="shared" si="56"/>
+        <v>257244</v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="56"/>
+        <v>262378</v>
+      </c>
+      <c r="J81" s="1">
+        <f>J61-J78</f>
+        <v>274213</v>
+      </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -5115,12 +5210,36 @@
       <c r="AD81" s="1"/>
       <c r="AE81" s="1"/>
     </row>
-    <row r="82" spans="6:31" x14ac:dyDescent="0.2">
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1">
+        <f t="shared" ref="E82:F82" si="57">E60-E78</f>
+        <v>-466</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="57"/>
+        <v>4444</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" ref="G82:H82" si="58">G60-G78</f>
+        <v>8749</v>
+      </c>
+      <c r="H82" s="1">
+        <f t="shared" si="58"/>
+        <v>29758</v>
+      </c>
+      <c r="I82" s="1">
+        <f>I60-I78</f>
+        <v>41523</v>
+      </c>
+      <c r="J82" s="1">
+        <f>J60-J78</f>
+        <v>57637</v>
+      </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -5143,7 +5262,7 @@
       <c r="AD82" s="1"/>
       <c r="AE82" s="1"/>
     </row>
-    <row r="83" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -5171,7 +5290,7 @@
       <c r="AD83" s="1"/>
       <c r="AE83" s="1"/>
     </row>
-    <row r="84" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -5199,7 +5318,7 @@
       <c r="AD84" s="1"/>
       <c r="AE84" s="1"/>
     </row>
-    <row r="85" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -5227,7 +5346,7 @@
       <c r="AD85" s="1"/>
       <c r="AE85" s="1"/>
     </row>
-    <row r="86" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -5255,7 +5374,7 @@
       <c r="AD86" s="1"/>
       <c r="AE86" s="1"/>
     </row>
-    <row r="87" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -5283,7 +5402,7 @@
       <c r="AD87" s="1"/>
       <c r="AE87" s="1"/>
     </row>
-    <row r="88" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -5311,7 +5430,7 @@
       <c r="AD88" s="1"/>
       <c r="AE88" s="1"/>
     </row>
-    <row r="89" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -5339,7 +5458,7 @@
       <c r="AD89" s="1"/>
       <c r="AE89" s="1"/>
     </row>
-    <row r="90" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -5367,7 +5486,7 @@
       <c r="AD90" s="1"/>
       <c r="AE90" s="1"/>
     </row>
-    <row r="91" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -5395,7 +5514,7 @@
       <c r="AD91" s="1"/>
       <c r="AE91" s="1"/>
     </row>
-    <row r="92" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -5423,7 +5542,7 @@
       <c r="AD92" s="1"/>
       <c r="AE92" s="1"/>
     </row>
-    <row r="93" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -5451,7 +5570,7 @@
       <c r="AD93" s="1"/>
       <c r="AE93" s="1"/>
     </row>
-    <row r="94" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -5479,7 +5598,7 @@
       <c r="AD94" s="1"/>
       <c r="AE94" s="1"/>
     </row>
-    <row r="95" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -5507,7 +5626,7 @@
       <c r="AD95" s="1"/>
       <c r="AE95" s="1"/>
     </row>
-    <row r="96" spans="6:31" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -9903,6 +10022,90 @@
       <c r="AD252" s="1"/>
       <c r="AE252" s="1"/>
     </row>
+    <row r="253" spans="6:31" x14ac:dyDescent="0.2">
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="K253" s="1"/>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+      <c r="N253" s="1"/>
+      <c r="O253" s="1"/>
+      <c r="P253" s="1"/>
+      <c r="Q253" s="1"/>
+      <c r="R253" s="1"/>
+      <c r="S253" s="1"/>
+      <c r="T253" s="1"/>
+      <c r="U253" s="1"/>
+      <c r="V253" s="1"/>
+      <c r="W253" s="1"/>
+      <c r="X253" s="1"/>
+      <c r="Y253" s="1"/>
+      <c r="Z253" s="1"/>
+      <c r="AA253" s="1"/>
+      <c r="AB253" s="1"/>
+      <c r="AC253" s="1"/>
+      <c r="AD253" s="1"/>
+      <c r="AE253" s="1"/>
+    </row>
+    <row r="254" spans="6:31" x14ac:dyDescent="0.2">
+      <c r="F254" s="1"/>
+      <c r="G254" s="1"/>
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+      <c r="K254" s="1"/>
+      <c r="L254" s="1"/>
+      <c r="M254" s="1"/>
+      <c r="N254" s="1"/>
+      <c r="O254" s="1"/>
+      <c r="P254" s="1"/>
+      <c r="Q254" s="1"/>
+      <c r="R254" s="1"/>
+      <c r="S254" s="1"/>
+      <c r="T254" s="1"/>
+      <c r="U254" s="1"/>
+      <c r="V254" s="1"/>
+      <c r="W254" s="1"/>
+      <c r="X254" s="1"/>
+      <c r="Y254" s="1"/>
+      <c r="Z254" s="1"/>
+      <c r="AA254" s="1"/>
+      <c r="AB254" s="1"/>
+      <c r="AC254" s="1"/>
+      <c r="AD254" s="1"/>
+      <c r="AE254" s="1"/>
+    </row>
+    <row r="255" spans="6:31" x14ac:dyDescent="0.2">
+      <c r="F255" s="1"/>
+      <c r="G255" s="1"/>
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
+      <c r="K255" s="1"/>
+      <c r="L255" s="1"/>
+      <c r="M255" s="1"/>
+      <c r="N255" s="1"/>
+      <c r="O255" s="1"/>
+      <c r="P255" s="1"/>
+      <c r="Q255" s="1"/>
+      <c r="R255" s="1"/>
+      <c r="S255" s="1"/>
+      <c r="T255" s="1"/>
+      <c r="U255" s="1"/>
+      <c r="V255" s="1"/>
+      <c r="W255" s="1"/>
+      <c r="X255" s="1"/>
+      <c r="Y255" s="1"/>
+      <c r="Z255" s="1"/>
+      <c r="AA255" s="1"/>
+      <c r="AB255" s="1"/>
+      <c r="AC255" s="1"/>
+      <c r="AD255" s="1"/>
+      <c r="AE255" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
